--- a/Results/eda_numeric_summary_by_target.xlsx
+++ b/Results/eda_numeric_summary_by_target.xlsx
@@ -14,7 +14,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>N_measured</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
   <si>
     <t>age</t>
   </si>
@@ -29,27 +47,6 @@
   </si>
   <si>
     <t>oldpeak</t>
-  </si>
-  <si>
-    <t>count</t>
-  </si>
-  <si>
-    <t>mean</t>
-  </si>
-  <si>
-    <t>std</t>
-  </si>
-  <si>
-    <t>median</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>max</t>
-  </si>
-  <si>
-    <t>target</t>
   </si>
 </sst>
 </file>
@@ -407,348 +404,230 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
-      <c r="A1" s="1"/>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="C2">
+        <v>410</v>
+      </c>
+      <c r="D2">
+        <v>50.55121951219513</v>
+      </c>
+      <c r="E2">
+        <v>9.444914854145766</v>
+      </c>
+      <c r="F2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-    </row>
-    <row r="2" spans="1:31">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C3">
+        <v>508</v>
+      </c>
+      <c r="D3">
+        <v>55.8996062992126</v>
+      </c>
+      <c r="E3">
+        <v>8.727055566369488</v>
+      </c>
+      <c r="F3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>410</v>
+      </c>
+      <c r="D4">
+        <v>130.1804878048781</v>
+      </c>
+      <c r="E4">
+        <v>16.49958463598395</v>
+      </c>
+      <c r="F4">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>507</v>
+      </c>
+      <c r="D5">
+        <v>134.4497041420118</v>
+      </c>
+      <c r="E5">
+        <v>18.92879665477102</v>
+      </c>
+      <c r="F5">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>390</v>
+      </c>
+      <c r="D6">
+        <v>238.7692307692308</v>
+      </c>
+      <c r="E6">
+        <v>55.3946168435367</v>
+      </c>
+      <c r="F6">
+        <v>231.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>356</v>
+      </c>
+      <c r="D7">
+        <v>251.061797752809</v>
+      </c>
+      <c r="E7">
+        <v>62.46271316935641</v>
+      </c>
+      <c r="F7">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>410</v>
+      </c>
+      <c r="D8">
+        <v>148.1512195121951</v>
+      </c>
+      <c r="E8">
+        <v>23.28806657848439</v>
+      </c>
+      <c r="F8">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>508</v>
+      </c>
+      <c r="D9">
+        <v>127.6555118110236</v>
+      </c>
+      <c r="E9">
+        <v>23.38692273396304</v>
+      </c>
+      <c r="F9">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>410</v>
+      </c>
+      <c r="D10">
+        <v>0.4080487804878049</v>
+      </c>
+      <c r="E10">
+        <v>0.6997090541438147</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31">
-      <c r="A4" s="1">
-        <v>0</v>
-      </c>
-      <c r="B4">
-        <v>548</v>
-      </c>
-      <c r="C4">
-        <v>52.075</v>
-      </c>
-      <c r="D4">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="E4">
-        <v>53</v>
-      </c>
-      <c r="F4">
-        <v>28</v>
-      </c>
-      <c r="G4">
-        <v>77</v>
-      </c>
-      <c r="H4">
-        <v>548</v>
-      </c>
-      <c r="I4">
-        <v>131.243</v>
-      </c>
-      <c r="J4">
-        <v>17.169</v>
-      </c>
-      <c r="K4">
-        <v>130</v>
-      </c>
-      <c r="L4">
-        <v>80</v>
-      </c>
-      <c r="M4">
-        <v>200</v>
-      </c>
-      <c r="N4">
-        <v>528</v>
-      </c>
-      <c r="O4">
-        <v>241.989</v>
-      </c>
-      <c r="P4">
-        <v>54.131</v>
-      </c>
-      <c r="Q4">
-        <v>236</v>
-      </c>
-      <c r="R4">
-        <v>85</v>
-      </c>
-      <c r="S4">
-        <v>564</v>
-      </c>
-      <c r="T4">
-        <v>548</v>
-      </c>
-      <c r="U4">
-        <v>145.872</v>
-      </c>
-      <c r="V4">
-        <v>23.428</v>
-      </c>
-      <c r="W4">
-        <v>148</v>
-      </c>
-      <c r="X4">
-        <v>69</v>
-      </c>
-      <c r="Y4">
-        <v>202</v>
-      </c>
-      <c r="Z4">
-        <v>548</v>
-      </c>
-      <c r="AA4">
-        <v>0.705</v>
-      </c>
-      <c r="AB4">
-        <v>1.025</v>
-      </c>
-      <c r="AC4">
-        <v>0.1</v>
-      </c>
-      <c r="AD4">
-        <v>-1.1</v>
-      </c>
-      <c r="AE4">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31">
-      <c r="A5" s="1">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="B5">
-        <v>672</v>
-      </c>
-      <c r="C5">
-        <v>55.091</v>
-      </c>
-      <c r="D5">
-        <v>9.031000000000001</v>
-      </c>
-      <c r="E5">
-        <v>56</v>
-      </c>
-      <c r="F5">
-        <v>29</v>
-      </c>
-      <c r="G5">
-        <v>77</v>
-      </c>
-      <c r="H5">
-        <v>671</v>
-      </c>
-      <c r="I5">
-        <v>133.179</v>
-      </c>
-      <c r="J5">
-        <v>18.425</v>
-      </c>
-      <c r="K5">
-        <v>130</v>
-      </c>
-      <c r="L5">
-        <v>92</v>
-      </c>
-      <c r="M5">
-        <v>200</v>
-      </c>
-      <c r="N5">
-        <v>520</v>
-      </c>
-      <c r="O5">
-        <v>248.406</v>
-      </c>
-      <c r="P5">
-        <v>59.846</v>
-      </c>
-      <c r="Q5">
-        <v>242</v>
-      </c>
-      <c r="R5">
-        <v>100</v>
-      </c>
-      <c r="S5">
-        <v>603</v>
-      </c>
-      <c r="T5">
-        <v>672</v>
-      </c>
-      <c r="U5">
-        <v>135.153</v>
-      </c>
-      <c r="V5">
-        <v>26.023</v>
-      </c>
-      <c r="W5">
-        <v>134</v>
-      </c>
-      <c r="X5">
-        <v>60</v>
-      </c>
-      <c r="Y5">
-        <v>202</v>
-      </c>
-      <c r="Z5">
-        <v>672</v>
-      </c>
-      <c r="AA5">
-        <v>1.106</v>
-      </c>
-      <c r="AB5">
-        <v>1.113</v>
-      </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AD5">
-        <v>-2.6</v>
-      </c>
-      <c r="AE5">
-        <v>6.2</v>
+      <c r="C11">
+        <v>508</v>
+      </c>
+      <c r="D11">
+        <v>1.274212598425197</v>
+      </c>
+      <c r="E11">
+        <v>1.151871973558762</v>
+      </c>
+      <c r="F11">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:S1"/>
-    <mergeCell ref="T1:Y1"/>
-    <mergeCell ref="Z1:AE1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>